--- a/Projects/Datasets for Excel/Datasets for excel/topbottom.xlsx
+++ b/Projects/Datasets for Excel/Datasets for excel/topbottom.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shahriar/Desktop/PROJECTs/Course/Data - Excel/8. highlight cells/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DS\tezendra\Projects\Datasets for Excel\Datasets for excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B26AA5C-3B21-EE47-8B50-588AD121372F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09480F1B-B7D3-49E5-A002-D1FBCF37D93A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$201</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
@@ -115,7 +118,46 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -415,15 +457,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:D201"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="12.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12.125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -437,7 +480,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -451,7 +494,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -465,7 +508,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -479,7 +522,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -493,7 +536,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -507,7 +550,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -521,21 +564,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>7</v>
+        <v>114</v>
       </c>
       <c r="B8" s="3">
-        <v>578.9606407753696</v>
+        <v>623.16210562426431</v>
       </c>
       <c r="C8" s="3">
-        <v>315.45105801625982</v>
+        <v>324.40528908001909</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -549,7 +592,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -563,7 +606,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -577,7 +620,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -591,7 +634,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -605,21 +648,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B14" s="3">
-        <v>512.09811357830176</v>
+        <v>578.9606407753696</v>
       </c>
       <c r="C14" s="3">
-        <v>328.62005290479613</v>
+        <v>315.45105801625982</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -633,7 +676,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -647,7 +690,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -661,7 +704,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -675,7 +718,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -689,7 +732,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -703,35 +746,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" s="3">
-        <v>429.38481493323542</v>
+        <v>573.28243844607766</v>
       </c>
       <c r="C21" s="3">
-        <v>302.45622418158968</v>
+        <v>369.43975700020519</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>21</v>
+        <v>163</v>
       </c>
       <c r="B22" s="3">
-        <v>573.28243844607766</v>
+        <v>557.92977895037018</v>
       </c>
       <c r="C22" s="3">
-        <v>369.43975700020519</v>
+        <v>296.73719554629429</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -745,7 +788,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -759,7 +802,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -773,21 +816,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="B26" s="3">
-        <v>472.78086377374092</v>
+        <v>550.17664489460117</v>
       </c>
       <c r="C26" s="3">
-        <v>285.84204402631701</v>
+        <v>257.09575866118098</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -801,21 +844,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>27</v>
+        <v>165</v>
       </c>
       <c r="B28" s="3">
-        <v>442.45032112888492</v>
+        <v>548.16880646221614</v>
       </c>
       <c r="C28" s="3">
-        <v>301.92840057286389</v>
+        <v>320.7043197513334</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -829,7 +872,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -843,7 +886,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -857,7 +900,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -871,7 +914,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -885,21 +928,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="B34" s="3">
-        <v>499.32513876310333</v>
+        <v>546.56400595580988</v>
       </c>
       <c r="C34" s="3">
-        <v>301.36715519711441</v>
+        <v>285.47297781401238</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -913,7 +956,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -927,7 +970,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -941,7 +984,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -955,21 +998,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="B39" s="3">
-        <v>402.01649380601123</v>
+        <v>541.09512521876115</v>
       </c>
       <c r="C39" s="3">
-        <v>305.59362944308282</v>
+        <v>313.86310422789808</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -983,7 +1026,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -997,7 +1040,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1011,7 +1054,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1025,77 +1068,77 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>43</v>
+        <v>162</v>
       </c>
       <c r="B44" s="3">
-        <v>494.21758588058799</v>
+        <v>539.35423018712265</v>
       </c>
       <c r="C44" s="3">
-        <v>315.1496183694137</v>
+        <v>345.98216739007728</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>44</v>
+        <v>166</v>
       </c>
       <c r="B45" s="3">
-        <v>484.94481522053559</v>
+        <v>520.6390463468249</v>
       </c>
       <c r="C45" s="3">
-        <v>325.97265582510357</v>
+        <v>287.96338584342487</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>45</v>
+        <v>196</v>
       </c>
       <c r="B46" s="3">
-        <v>426.07390048162858</v>
+        <v>519.26586898644189</v>
       </c>
       <c r="C46" s="3">
-        <v>263.9911077883267</v>
+        <v>285.92473043685891</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="B47" s="3">
-        <v>464.00778958026461</v>
+        <v>518.08180125238175</v>
       </c>
       <c r="C47" s="3">
-        <v>289.96496292477161</v>
+        <v>286.79866539909051</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>47</v>
+        <v>152</v>
       </c>
       <c r="B48" s="3">
-        <v>476.9680614520106</v>
+        <v>517.32241047484877</v>
       </c>
       <c r="C48" s="3">
-        <v>285.75164066517129</v>
+        <v>344.26068650848657</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1109,7 +1152,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1123,21 +1166,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>50</v>
+        <v>174</v>
       </c>
       <c r="B51" s="3">
-        <v>411.84799223186332</v>
+        <v>517.05759874083219</v>
       </c>
       <c r="C51" s="3">
-        <v>312.14945132882872</v>
+        <v>328.77812478255618</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1151,7 +1194,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1165,21 +1208,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="B54" s="3">
-        <v>466.15389998470209</v>
+        <v>515.07736711668065</v>
       </c>
       <c r="C54" s="3">
-        <v>363.66468591037898</v>
+        <v>300.63011524898269</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1193,7 +1236,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1207,35 +1250,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>56</v>
+        <v>150</v>
       </c>
       <c r="B57" s="3">
-        <v>546.56400595580988</v>
+        <v>514.84923366165935</v>
       </c>
       <c r="C57" s="3">
-        <v>285.47297781401238</v>
+        <v>293.59658544864459</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>57</v>
+        <v>145</v>
       </c>
       <c r="B58" s="3">
-        <v>458.03912383886808</v>
+        <v>512.9941397124212</v>
       </c>
       <c r="C58" s="3">
-        <v>338.00733447559873</v>
+        <v>285.86885083145029</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1249,7 +1292,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1263,7 +1306,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1277,7 +1320,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -1291,7 +1334,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -1305,7 +1348,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -1319,7 +1362,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -1333,7 +1376,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -1347,7 +1390,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -1361,7 +1404,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -1375,35 +1418,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="B69" s="3">
-        <v>550.17664489460117</v>
+        <v>512.09811357830176</v>
       </c>
       <c r="C69" s="3">
-        <v>257.09575866118098</v>
+        <v>328.62005290479613</v>
       </c>
       <c r="D69" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>69</v>
+        <v>154</v>
       </c>
       <c r="B70" s="3">
-        <v>518.08180125238175</v>
+        <v>511.61268485805022</v>
       </c>
       <c r="C70" s="3">
-        <v>286.79866539909051</v>
+        <v>295.20184410109721</v>
       </c>
       <c r="D70" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -1417,7 +1460,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -1431,7 +1474,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -1445,21 +1488,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>73</v>
+        <v>195</v>
       </c>
       <c r="B74" s="3">
-        <v>498.2086980445024</v>
+        <v>508.65904629255908</v>
       </c>
       <c r="C74" s="3">
-        <v>334.89491256464879</v>
+        <v>335.38320362163859</v>
       </c>
       <c r="D74" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -1473,7 +1516,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -1487,91 +1530,91 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>76</v>
+        <v>129</v>
       </c>
       <c r="B77" s="3">
-        <v>541.09512521876115</v>
+        <v>504.98256825438199</v>
       </c>
       <c r="C77" s="3">
-        <v>313.86310422789808</v>
+        <v>318.72359451156473</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78">
+        <v>79</v>
+      </c>
+      <c r="B78" s="3">
+        <v>504.58803882677512</v>
+      </c>
+      <c r="C78" s="3">
+        <v>302.0940625497006</v>
+      </c>
+      <c r="D78" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79">
         <v>77</v>
       </c>
-      <c r="B78" s="3">
+      <c r="B79" s="3">
         <v>504.35235341190861</v>
       </c>
-      <c r="C78" s="3">
+      <c r="C79" s="3">
         <v>305.97179086720411</v>
       </c>
-      <c r="D78" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79">
-        <v>78</v>
-      </c>
-      <c r="B79" s="3">
-        <v>485.04963247670662</v>
-      </c>
-      <c r="C79" s="3">
-        <v>281.99349368523622</v>
-      </c>
       <c r="D79" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>79</v>
+        <v>177</v>
       </c>
       <c r="B80" s="3">
-        <v>504.58803882677512</v>
+        <v>500.65009459389529</v>
       </c>
       <c r="C80" s="3">
-        <v>302.0940625497006</v>
+        <v>326.16961910162041</v>
       </c>
       <c r="D80" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="B81" s="3">
-        <v>400.62155426995542</v>
+        <v>499.32513876310333</v>
       </c>
       <c r="C81" s="3">
-        <v>288.44059209414718</v>
+        <v>301.36715519711441</v>
       </c>
       <c r="D81" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="B82" s="3">
-        <v>489.01640560812439</v>
+        <v>498.67430622753909</v>
       </c>
       <c r="C82" s="3">
-        <v>303.40552035753751</v>
+        <v>332.96330555961572</v>
       </c>
       <c r="D82" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -1585,7 +1628,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -1599,7 +1642,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -1613,7 +1656,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -1627,21 +1670,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="B87" s="3">
-        <v>474.91214782077321</v>
+        <v>498.2086980445024</v>
       </c>
       <c r="C87" s="3">
-        <v>241.43736601432491</v>
+        <v>334.89491256464879</v>
       </c>
       <c r="D87" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -1655,7 +1698,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -1669,21 +1712,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="B90" s="3">
-        <v>473.51198981164799</v>
+        <v>494.21758588058799</v>
       </c>
       <c r="C90" s="3">
-        <v>308.42975603205099</v>
+        <v>315.1496183694137</v>
       </c>
       <c r="D90" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -1697,7 +1740,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -1711,7 +1754,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -1725,7 +1768,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -1739,21 +1782,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="B95" s="3">
-        <v>483.61689267011161</v>
+        <v>491.93571441669962</v>
       </c>
       <c r="C95" s="3">
-        <v>325.48806291063067</v>
+        <v>299.37295218107562</v>
       </c>
       <c r="D95" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -1767,21 +1810,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="B97" s="3">
-        <v>426.82425259339408</v>
+        <v>489.01640560812439</v>
       </c>
       <c r="C97" s="3">
-        <v>279.21271214218041</v>
+        <v>303.40552035753751</v>
       </c>
       <c r="D97" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -1795,7 +1838,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -1809,7 +1852,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -1823,7 +1866,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -1837,7 +1880,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -1851,21 +1894,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="B103" s="3">
-        <v>478.96773386173197</v>
+        <v>485.04963247670662</v>
       </c>
       <c r="C103" s="3">
-        <v>283.19456879409091</v>
+        <v>281.99349368523622</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -1879,7 +1922,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -1893,21 +1936,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="B106" s="3">
-        <v>491.93571441669962</v>
+        <v>484.94481522053559</v>
       </c>
       <c r="C106" s="3">
-        <v>299.37295218107562</v>
+        <v>325.97265582510357</v>
       </c>
       <c r="D106" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -1921,7 +1964,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -1935,7 +1978,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -1949,7 +1992,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -1963,7 +2006,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -1977,35 +2020,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="B112" s="3">
-        <v>404.06143923504789</v>
+        <v>483.61689267011161</v>
       </c>
       <c r="C112" s="3">
-        <v>293.46956390318343</v>
+        <v>325.48806291063067</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B113" s="3">
-        <v>498.67430622753909</v>
+        <v>478.96773386173197</v>
       </c>
       <c r="C113" s="3">
-        <v>332.96330555961572</v>
+        <v>283.19456879409091</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -2019,21 +2062,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>114</v>
+        <v>47</v>
       </c>
       <c r="B115" s="3">
-        <v>623.16210562426431</v>
+        <v>476.9680614520106</v>
       </c>
       <c r="C115" s="3">
-        <v>324.40528908001909</v>
+        <v>285.75164066517129</v>
       </c>
       <c r="D115" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -2047,21 +2090,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="B117" s="3">
-        <v>515.07736711668065</v>
+        <v>474.91214782077321</v>
       </c>
       <c r="C117" s="3">
-        <v>300.63011524898269</v>
+        <v>241.43736601432491</v>
       </c>
       <c r="D117" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
@@ -2075,7 +2118,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
@@ -2089,7 +2132,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
@@ -2103,7 +2146,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -2117,7 +2160,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -2131,7 +2174,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
@@ -2145,7 +2188,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
@@ -2159,7 +2202,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
@@ -2173,7 +2216,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
@@ -2187,7 +2230,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
@@ -2201,7 +2244,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
@@ -2215,7 +2258,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
@@ -2229,21 +2272,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="B130" s="3">
-        <v>504.98256825438199</v>
+        <v>473.51198981164799</v>
       </c>
       <c r="C130" s="3">
-        <v>318.72359451156473</v>
+        <v>308.42975603205099</v>
       </c>
       <c r="D130" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
@@ -2257,7 +2300,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
@@ -2271,7 +2314,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
@@ -2285,7 +2328,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
@@ -2299,7 +2342,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
@@ -2313,7 +2356,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
@@ -2327,7 +2370,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
@@ -2341,7 +2384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
@@ -2355,7 +2398,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
@@ -2369,7 +2412,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
@@ -2383,7 +2426,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
@@ -2397,7 +2440,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
@@ -2411,7 +2454,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
@@ -2425,21 +2468,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>143</v>
+        <v>25</v>
       </c>
       <c r="B144" s="3">
-        <v>419.62583827193862</v>
+        <v>472.78086377374092</v>
       </c>
       <c r="C144" s="3">
-        <v>307.34899713326172</v>
+        <v>285.84204402631701</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
@@ -2453,21 +2496,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="B146" s="3">
-        <v>512.9941397124212</v>
+        <v>466.15389998470209</v>
       </c>
       <c r="C146" s="3">
-        <v>285.86885083145029</v>
+        <v>363.66468591037898</v>
       </c>
       <c r="D146" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
@@ -2481,7 +2524,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>147</v>
       </c>
@@ -2495,7 +2538,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
@@ -2509,7 +2552,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>149</v>
       </c>
@@ -2523,21 +2566,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B151" s="3">
-        <v>514.84923366165935</v>
+        <v>464.28242909868158</v>
       </c>
       <c r="C151" s="3">
-        <v>293.59658544864459</v>
+        <v>269.92411906086568</v>
       </c>
       <c r="D151" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>151</v>
       </c>
@@ -2551,21 +2594,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>152</v>
+        <v>46</v>
       </c>
       <c r="B153" s="3">
-        <v>517.32241047484877</v>
+        <v>464.00778958026461</v>
       </c>
       <c r="C153" s="3">
-        <v>344.26068650848657</v>
+        <v>289.96496292477161</v>
       </c>
       <c r="D153" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>153</v>
       </c>
@@ -2579,21 +2622,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="B155" s="3">
-        <v>511.61268485805022</v>
+        <v>462.3131917821255</v>
       </c>
       <c r="C155" s="3">
-        <v>295.20184410109721</v>
+        <v>276.809706484336</v>
       </c>
       <c r="D155" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>155</v>
       </c>
@@ -2607,21 +2650,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>156</v>
+        <v>57</v>
       </c>
       <c r="B157" s="3">
-        <v>464.28242909868158</v>
+        <v>458.03912383886808</v>
       </c>
       <c r="C157" s="3">
-        <v>269.92411906086568</v>
+        <v>338.00733447559873</v>
       </c>
       <c r="D157" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>157</v>
       </c>
@@ -2635,7 +2678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>158</v>
       </c>
@@ -2649,7 +2692,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>159</v>
       </c>
@@ -2663,7 +2706,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>160</v>
       </c>
@@ -2677,49 +2720,49 @@
         <v>6</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162">
+        <v>197</v>
+      </c>
+      <c r="B162" s="3">
+        <v>455.80712818994328</v>
+      </c>
+      <c r="C162" s="3">
+        <v>248.60596412727369</v>
+      </c>
+      <c r="D162" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163">
         <v>161</v>
       </c>
-      <c r="B162" s="3">
+      <c r="B163" s="3">
         <v>451.26591648863388</v>
       </c>
-      <c r="C162" s="3">
+      <c r="C163" s="3">
         <v>315.58039542723509</v>
       </c>
-      <c r="D162" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A163">
-        <v>162</v>
-      </c>
-      <c r="B163" s="3">
-        <v>539.35423018712265</v>
-      </c>
-      <c r="C163" s="3">
-        <v>345.98216739007728</v>
-      </c>
       <c r="D163" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="B164" s="3">
-        <v>557.92977895037018</v>
+        <v>446.45537509694441</v>
       </c>
       <c r="C164" s="3">
-        <v>296.73719554629429</v>
+        <v>236.28312827070579</v>
       </c>
       <c r="D164" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>164</v>
       </c>
@@ -2733,35 +2776,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="B166" s="3">
-        <v>548.16880646221614</v>
+        <v>442.85148510846892</v>
       </c>
       <c r="C166" s="3">
-        <v>320.7043197513334</v>
+        <v>337.13448935920383</v>
       </c>
       <c r="D166" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>166</v>
+        <v>27</v>
       </c>
       <c r="B167" s="3">
-        <v>520.6390463468249</v>
+        <v>442.45032112888492</v>
       </c>
       <c r="C167" s="3">
-        <v>287.96338584342487</v>
+        <v>301.92840057286389</v>
       </c>
       <c r="D167" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>167</v>
       </c>
@@ -2775,7 +2818,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>168</v>
       </c>
@@ -2789,7 +2832,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>169</v>
       </c>
@@ -2803,21 +2846,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>170</v>
+        <v>20</v>
       </c>
       <c r="B171" s="3">
-        <v>462.3131917821255</v>
+        <v>429.38481493323542</v>
       </c>
       <c r="C171" s="3">
-        <v>276.809706484336</v>
+        <v>302.45622418158968</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>171</v>
       </c>
@@ -2831,7 +2874,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>172</v>
       </c>
@@ -2845,7 +2888,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>173</v>
       </c>
@@ -2859,21 +2902,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>174</v>
+        <v>96</v>
       </c>
       <c r="B175" s="3">
-        <v>517.05759874083219</v>
+        <v>426.82425259339408</v>
       </c>
       <c r="C175" s="3">
-        <v>328.77812478255618</v>
+        <v>279.21271214218041</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>175</v>
       </c>
@@ -2887,7 +2930,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>176</v>
       </c>
@@ -2901,21 +2944,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178">
-        <v>177</v>
+        <v>45</v>
       </c>
       <c r="B178" s="3">
-        <v>500.65009459389529</v>
+        <v>426.07390048162858</v>
       </c>
       <c r="C178" s="3">
-        <v>326.16961910162041</v>
+        <v>263.9911077883267</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>178</v>
       </c>
@@ -2929,7 +2972,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>179</v>
       </c>
@@ -2943,7 +2986,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>180</v>
       </c>
@@ -2957,7 +3000,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>181</v>
       </c>
@@ -2971,7 +3014,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>182</v>
       </c>
@@ -2985,21 +3028,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>183</v>
+        <v>143</v>
       </c>
       <c r="B184" s="3">
-        <v>446.45537509694441</v>
+        <v>419.62583827193862</v>
       </c>
       <c r="C184" s="3">
-        <v>236.28312827070579</v>
+        <v>307.34899713326172</v>
       </c>
       <c r="D184" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>184</v>
       </c>
@@ -3013,7 +3056,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>185</v>
       </c>
@@ -3027,7 +3070,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>186</v>
       </c>
@@ -3041,7 +3084,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>187</v>
       </c>
@@ -3055,7 +3098,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>188</v>
       </c>
@@ -3069,7 +3112,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>189</v>
       </c>
@@ -3083,7 +3126,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>190</v>
       </c>
@@ -3097,7 +3140,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>191</v>
       </c>
@@ -3111,7 +3154,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>192</v>
       </c>
@@ -3125,7 +3168,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>193</v>
       </c>
@@ -3139,7 +3182,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>194</v>
       </c>
@@ -3153,49 +3196,49 @@
         <v>6</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196">
-        <v>195</v>
+        <v>50</v>
       </c>
       <c r="B196" s="3">
-        <v>508.65904629255908</v>
+        <v>411.84799223186332</v>
       </c>
       <c r="C196" s="3">
-        <v>335.38320362163859</v>
+        <v>312.14945132882872</v>
       </c>
       <c r="D196" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="B197" s="3">
-        <v>519.26586898644189</v>
+        <v>404.06143923504789</v>
       </c>
       <c r="C197" s="3">
-        <v>285.92473043685891</v>
+        <v>293.46956390318343</v>
       </c>
       <c r="D197" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198">
-        <v>197</v>
+        <v>38</v>
       </c>
       <c r="B198" s="3">
-        <v>455.80712818994328</v>
+        <v>402.01649380601123</v>
       </c>
       <c r="C198" s="3">
-        <v>248.60596412727369</v>
+        <v>305.59362944308282</v>
       </c>
       <c r="D198" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>198</v>
       </c>
@@ -3209,7 +3252,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>199</v>
       </c>
@@ -3223,21 +3266,39 @@
         <v>4</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="B201" s="3">
-        <v>442.85148510846892</v>
+        <v>400.62155426995542</v>
       </c>
       <c r="C201" s="3">
-        <v>337.13448935920383</v>
+        <v>288.44059209414718</v>
       </c>
       <c r="D201" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D201" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <colorFilter dxfId="0"/>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:D201">
+      <sortCondition descending="1" ref="B1:B201"/>
+    </sortState>
+  </autoFilter>
+  <conditionalFormatting sqref="D1">
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Home &amp; Kitchen">
+      <formula>NOT(ISERROR(SEARCH("Home &amp; Kitchen",D1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Home">
+      <formula>NOT(ISERROR(SEARCH("Home",D1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>